--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>78.30145614513103</v>
+        <v>12.72398662358379</v>
       </c>
       <c r="D2" t="n">
-        <v>45.75186011489028</v>
+        <v>7.43467726866967</v>
       </c>
       <c r="E2" t="n">
-        <v>20.62518532230413</v>
+        <v>3.351592614874422</v>
       </c>
       <c r="F2" t="n">
-        <v>6.558417855315406</v>
+        <v>1.065742901488753</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.35006664094077</v>
+        <v>4.769385829152876</v>
       </c>
       <c r="D3" t="n">
-        <v>29.17872603262193</v>
+        <v>4.741542980301064</v>
       </c>
       <c r="E3" t="n">
-        <v>20.62518532230413</v>
+        <v>3.351592614874422</v>
       </c>
       <c r="F3" t="n">
-        <v>6.558417855315406</v>
+        <v>1.065742901488753</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.49952243425174</v>
+        <v>4.793672395565909</v>
       </c>
       <c r="D4" t="n">
-        <v>30.45407126510043</v>
+        <v>4.94878658057882</v>
       </c>
       <c r="E4" t="n">
-        <v>20.62518532230413</v>
+        <v>3.351592614874422</v>
       </c>
       <c r="F4" t="n">
-        <v>6.558417855315406</v>
+        <v>1.065742901488753</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.66362219736183</v>
+        <v>5.470338607071298</v>
       </c>
       <c r="D5" t="n">
-        <v>33.51762715314395</v>
+        <v>5.446614412385892</v>
       </c>
       <c r="E5" t="n">
-        <v>20.62518532230413</v>
+        <v>3.351592614874422</v>
       </c>
       <c r="F5" t="n">
-        <v>6.558417855315406</v>
+        <v>1.065742901488753</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
